--- a/resources/templates/standard/A3200-01.xlsx
+++ b/resources/templates/standard/A3200-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="17">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>이해 관계자 불만 조치대장</t>
   </si>
@@ -599,12 +602,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -626,7 +631,7 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
@@ -700,21 +705,21 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -722,7 +727,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
@@ -730,7 +735,7 @@
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
       <c r="U4" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -738,7 +743,7 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AA4" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
@@ -772,11 +777,11 @@
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
       <c r="AA5" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD5" s="7"/>
     </row>
@@ -880,7 +885,7 @@
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -914,7 +919,7 @@
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -925,7 +930,7 @@
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
@@ -936,7 +941,7 @@
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
@@ -952,7 +957,7 @@
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -963,7 +968,7 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
@@ -974,7 +979,7 @@
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
       <c r="U11" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V11" s="10"/>
       <c r="W11" s="10"/>
@@ -1086,7 +1091,7 @@
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -1120,7 +1125,7 @@
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -1131,7 +1136,7 @@
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
@@ -1142,7 +1147,7 @@
       <c r="S16" s="9"/>
       <c r="T16" s="9"/>
       <c r="U16" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -1158,7 +1163,7 @@
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -1169,7 +1174,7 @@
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
@@ -1180,7 +1185,7 @@
       <c r="S17" s="13"/>
       <c r="T17" s="13"/>
       <c r="U17" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
@@ -1292,7 +1297,7 @@
       <c r="A21" s="14"/>
       <c r="B21" s="14"/>
       <c r="C21" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -1326,7 +1331,7 @@
       <c r="A22" s="14"/>
       <c r="B22" s="14"/>
       <c r="C22" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -1337,7 +1342,7 @@
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
@@ -1348,7 +1353,7 @@
       <c r="S22" s="9"/>
       <c r="T22" s="9"/>
       <c r="U22" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
@@ -1364,7 +1369,7 @@
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -1375,7 +1380,7 @@
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
       <c r="L23" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
@@ -1386,7 +1391,7 @@
       <c r="S23" s="10"/>
       <c r="T23" s="10"/>
       <c r="U23" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V23" s="10"/>
       <c r="W23" s="10"/>
@@ -1498,7 +1503,7 @@
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -1532,7 +1537,7 @@
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
@@ -1543,7 +1548,7 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
@@ -1554,7 +1559,7 @@
       <c r="S28" s="9"/>
       <c r="T28" s="9"/>
       <c r="U28" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
@@ -1570,7 +1575,7 @@
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -1581,7 +1586,7 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="13"/>
@@ -1592,7 +1597,7 @@
       <c r="S29" s="13"/>
       <c r="T29" s="13"/>
       <c r="U29" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
@@ -1704,7 +1709,7 @@
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -1738,7 +1743,7 @@
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="C34" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -1749,7 +1754,7 @@
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
@@ -1760,7 +1765,7 @@
       <c r="S34" s="9"/>
       <c r="T34" s="9"/>
       <c r="U34" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -1776,7 +1781,7 @@
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="C35" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
@@ -1787,7 +1792,7 @@
       <c r="J35" s="16"/>
       <c r="K35" s="16"/>
       <c r="L35" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
@@ -1798,7 +1803,7 @@
       <c r="S35" s="16"/>
       <c r="T35" s="16"/>
       <c r="U35" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V35" s="16"/>
       <c r="W35" s="16"/>
